--- a/data/WP17/WP17_auswertung_ministerien.xlsx
+++ b/data/WP17/WP17_auswertung_ministerien.xlsx
@@ -488,16 +488,16 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="D2" t="n">
-        <v>30.9614643545279</v>
+        <v>30.9298751200768</v>
       </c>
       <c r="E2" t="n">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F2" t="n">
-        <v>40.1923076923077</v>
+        <v>40.1536983669548</v>
       </c>
     </row>
     <row r="3">
@@ -511,7 +511,7 @@
         <v>944</v>
       </c>
       <c r="D3" t="n">
-        <v>33.9045599151644</v>
+        <v>33.8887711864407</v>
       </c>
       <c r="E3" t="n">
         <v>677</v>
@@ -551,13 +551,13 @@
         <v>658</v>
       </c>
       <c r="D5" t="n">
-        <v>31.1068702290076</v>
+        <v>31.1094224924012</v>
       </c>
       <c r="E5" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F5" t="n">
-        <v>35.258358662614</v>
+        <v>34.9544072948328</v>
       </c>
     </row>
     <row r="6">
@@ -608,16 +608,16 @@
         <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D8" t="n">
-        <v>27.377938517179</v>
+        <v>27.3842010771993</v>
       </c>
       <c r="E8" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F8" t="n">
-        <v>61.8705035971223</v>
+        <v>61.7594254937163</v>
       </c>
     </row>
     <row r="9">
@@ -808,16 +808,16 @@
         <v>39</v>
       </c>
       <c r="C18" t="n">
-        <v>6519</v>
+        <v>6521</v>
       </c>
       <c r="D18" t="n">
-        <v>31.2265745007681</v>
+        <v>31.2179113632878</v>
       </c>
       <c r="E18" t="n">
-        <v>3939</v>
+        <v>3943</v>
       </c>
       <c r="F18" t="n">
-        <v>39.5766221813162</v>
+        <v>39.5338138322343</v>
       </c>
     </row>
   </sheetData>
@@ -1054,13 +1054,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78C31CAC-36CB-497F-A1F4-C40B07EB693A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6E4F687-F722-471A-8EEF-E1392C9032D4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{012E55BE-B679-43E1-92CE-E7730F9624F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77E090DE-C407-4185-9681-EFB484DAD998}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28EBBB35-EFA9-4A8E-9F6A-5EC1B362792A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEF71D3C-4BEB-47CC-82F2-41CD02F26A78}"/>
 </file>
--- a/data/WP17/WP17_auswertung_ministerien.xlsx
+++ b/data/WP17/WP17_auswertung_ministerien.xlsx
@@ -491,13 +491,13 @@
         <v>1041</v>
       </c>
       <c r="D2" t="n">
-        <v>30.9298751200768</v>
+        <v>31.254562920269</v>
       </c>
       <c r="E2" t="n">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="F2" t="n">
-        <v>40.1536983669548</v>
+        <v>39.5773294908742</v>
       </c>
     </row>
     <row r="3">
@@ -511,13 +511,13 @@
         <v>944</v>
       </c>
       <c r="D3" t="n">
-        <v>33.8887711864407</v>
+        <v>33.6896186440678</v>
       </c>
       <c r="E3" t="n">
-        <v>677</v>
+        <v>665</v>
       </c>
       <c r="F3" t="n">
-        <v>28.2838983050847</v>
+        <v>29.5550847457627</v>
       </c>
     </row>
     <row r="4">
@@ -531,13 +531,13 @@
         <v>734</v>
       </c>
       <c r="D4" t="n">
-        <v>31.3351498637602</v>
+        <v>31.3801089918256</v>
       </c>
       <c r="E4" t="n">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="F4" t="n">
-        <v>48.2288828337875</v>
+        <v>46.3215258855586</v>
       </c>
     </row>
     <row r="5">
@@ -551,13 +551,13 @@
         <v>658</v>
       </c>
       <c r="D5" t="n">
-        <v>31.1094224924012</v>
+        <v>31.1747720364742</v>
       </c>
       <c r="E5" t="n">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="F5" t="n">
-        <v>34.9544072948328</v>
+        <v>33.5866261398176</v>
       </c>
     </row>
     <row r="6">
@@ -571,13 +571,13 @@
         <v>630</v>
       </c>
       <c r="D6" t="n">
-        <v>30.1095238095238</v>
+        <v>29.0920634920635</v>
       </c>
       <c r="E6" t="n">
-        <v>374</v>
+        <v>354</v>
       </c>
       <c r="F6" t="n">
-        <v>40.6349206349206</v>
+        <v>43.8095238095238</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         <v>622</v>
       </c>
       <c r="D7" t="n">
-        <v>31.2170418006431</v>
+        <v>31.4951768488746</v>
       </c>
       <c r="E7" t="n">
         <v>407</v>
@@ -611,13 +611,13 @@
         <v>557</v>
       </c>
       <c r="D8" t="n">
-        <v>27.3842010771993</v>
+        <v>27.0377019748653</v>
       </c>
       <c r="E8" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F8" t="n">
-        <v>61.7594254937163</v>
+        <v>62.2980251346499</v>
       </c>
     </row>
     <row r="9">
@@ -631,13 +631,13 @@
         <v>430</v>
       </c>
       <c r="D9" t="n">
-        <v>31.5162790697674</v>
+        <v>31.8325581395349</v>
       </c>
       <c r="E9" t="n">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="F9" t="n">
-        <v>34.8837209302326</v>
+        <v>31.3953488372093</v>
       </c>
     </row>
     <row r="10">
@@ -651,13 +651,13 @@
         <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>30.2217194570136</v>
+        <v>29.8552036199095</v>
       </c>
       <c r="E10" t="n">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="F10" t="n">
-        <v>41.6289592760181</v>
+        <v>48.4162895927602</v>
       </c>
     </row>
     <row r="11">
@@ -671,13 +671,13 @@
         <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>34.1803278688525</v>
+        <v>34.5846994535519</v>
       </c>
       <c r="E11" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="F11" t="n">
-        <v>34.9726775956284</v>
+        <v>29.5081967213115</v>
       </c>
     </row>
     <row r="12">
@@ -691,13 +691,13 @@
         <v>179</v>
       </c>
       <c r="D12" t="n">
-        <v>34.7374301675978</v>
+        <v>34.9664804469274</v>
       </c>
       <c r="E12" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F12" t="n">
-        <v>26.8156424581006</v>
+        <v>24.5810055865922</v>
       </c>
     </row>
     <row r="13">
@@ -711,7 +711,7 @@
         <v>167</v>
       </c>
       <c r="D13" t="n">
-        <v>29.2455089820359</v>
+        <v>29.4610778443114</v>
       </c>
       <c r="E13" t="n">
         <v>80</v>
@@ -731,13 +731,13 @@
         <v>149</v>
       </c>
       <c r="D14" t="n">
-        <v>30</v>
+        <v>27.9395973154362</v>
       </c>
       <c r="E14" t="n">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="F14" t="n">
-        <v>34.2281879194631</v>
+        <v>68.4563758389262</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +751,7 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>25.6666666666667</v>
+        <v>24.3333333333333</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -771,7 +771,7 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
@@ -791,7 +791,7 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -811,13 +811,13 @@
         <v>6521</v>
       </c>
       <c r="D18" t="n">
-        <v>31.2179113632878</v>
+        <v>31.1349486275111</v>
       </c>
       <c r="E18" t="n">
-        <v>3943</v>
+        <v>3900</v>
       </c>
       <c r="F18" t="n">
-        <v>39.5338138322343</v>
+        <v>40.1932218984818</v>
       </c>
     </row>
   </sheetData>
@@ -1054,13 +1054,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6E4F687-F722-471A-8EEF-E1392C9032D4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F30D4BBE-27EE-40AB-A9CC-088CAB86235C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77E090DE-C407-4185-9681-EFB484DAD998}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B74E32ED-6E67-4463-A53C-29760B32FC69}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEF71D3C-4BEB-47CC-82F2-41CD02F26A78}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D6D0328-51D9-4E04-83FA-8186D874E137}"/>
 </file>
--- a/data/WP17/WP17_auswertung_ministerien.xlsx
+++ b/data/WP17/WP17_auswertung_ministerien.xlsx
@@ -494,10 +494,10 @@
         <v>31.254562920269</v>
       </c>
       <c r="E2" t="n">
-        <v>629</v>
+        <v>723</v>
       </c>
       <c r="F2" t="n">
-        <v>39.5773294908742</v>
+        <v>30.5475504322767</v>
       </c>
     </row>
     <row r="3">
@@ -514,10 +514,10 @@
         <v>33.6896186440678</v>
       </c>
       <c r="E3" t="n">
-        <v>665</v>
+        <v>685</v>
       </c>
       <c r="F3" t="n">
-        <v>29.5550847457627</v>
+        <v>27.4364406779661</v>
       </c>
     </row>
     <row r="4">
@@ -534,10 +534,10 @@
         <v>31.3801089918256</v>
       </c>
       <c r="E4" t="n">
-        <v>394</v>
+        <v>450</v>
       </c>
       <c r="F4" t="n">
-        <v>46.3215258855586</v>
+        <v>38.6920980926431</v>
       </c>
     </row>
     <row r="5">
@@ -554,10 +554,10 @@
         <v>31.1747720364742</v>
       </c>
       <c r="E5" t="n">
-        <v>437</v>
+        <v>461</v>
       </c>
       <c r="F5" t="n">
-        <v>33.5866261398176</v>
+        <v>29.9392097264438</v>
       </c>
     </row>
     <row r="6">
@@ -574,10 +574,10 @@
         <v>29.0920634920635</v>
       </c>
       <c r="E6" t="n">
-        <v>354</v>
+        <v>417</v>
       </c>
       <c r="F6" t="n">
-        <v>43.8095238095238</v>
+        <v>33.8095238095238</v>
       </c>
     </row>
     <row r="7">
@@ -594,10 +594,10 @@
         <v>31.4951768488746</v>
       </c>
       <c r="E7" t="n">
-        <v>407</v>
+        <v>462</v>
       </c>
       <c r="F7" t="n">
-        <v>34.5659163987138</v>
+        <v>25.7234726688103</v>
       </c>
     </row>
     <row r="8">
@@ -614,10 +614,10 @@
         <v>27.0377019748653</v>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="F8" t="n">
-        <v>62.2980251346499</v>
+        <v>56.0143626570916</v>
       </c>
     </row>
     <row r="9">
@@ -634,10 +634,10 @@
         <v>31.8325581395349</v>
       </c>
       <c r="E9" t="n">
-        <v>295</v>
+        <v>334</v>
       </c>
       <c r="F9" t="n">
-        <v>31.3953488372093</v>
+        <v>22.3255813953488</v>
       </c>
     </row>
     <row r="10">
@@ -654,10 +654,10 @@
         <v>29.8552036199095</v>
       </c>
       <c r="E10" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F10" t="n">
-        <v>48.4162895927602</v>
+        <v>43.4389140271493</v>
       </c>
     </row>
     <row r="11">
@@ -674,10 +674,10 @@
         <v>34.5846994535519</v>
       </c>
       <c r="E11" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="F11" t="n">
-        <v>29.5081967213115</v>
+        <v>24.5901639344262</v>
       </c>
     </row>
     <row r="12">
@@ -694,10 +694,10 @@
         <v>34.9664804469274</v>
       </c>
       <c r="E12" t="n">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="F12" t="n">
-        <v>24.5810055865922</v>
+        <v>15.6424581005587</v>
       </c>
     </row>
     <row r="13">
@@ -714,10 +714,10 @@
         <v>29.4610778443114</v>
       </c>
       <c r="E13" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="F13" t="n">
-        <v>52.0958083832335</v>
+        <v>43.1137724550898</v>
       </c>
     </row>
     <row r="14">
@@ -734,10 +734,10 @@
         <v>27.9395973154362</v>
       </c>
       <c r="E14" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F14" t="n">
-        <v>68.4563758389262</v>
+        <v>64.4295302013423</v>
       </c>
     </row>
     <row r="15">
@@ -814,10 +814,10 @@
         <v>31.1349486275111</v>
       </c>
       <c r="E18" t="n">
-        <v>3900</v>
+        <v>4343</v>
       </c>
       <c r="F18" t="n">
-        <v>40.1932218984818</v>
+        <v>33.3997853090017</v>
       </c>
     </row>
   </sheetData>
@@ -1054,13 +1054,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F30D4BBE-27EE-40AB-A9CC-088CAB86235C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F3148ED-76A9-41EB-A27E-F5BB15952A07}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B74E32ED-6E67-4463-A53C-29760B32FC69}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5C68C4B-3221-4A09-9D7A-9094F6F5FEC0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D6D0328-51D9-4E04-83FA-8186D874E137}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D69DF740-2EC6-484A-8826-9552ADDF5E88}"/>
 </file>